--- a/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
@@ -647,28 +647,28 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>31</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>9.4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -679,28 +679,28 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>31</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
         <v>9.4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -851,28 +851,28 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>31</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -883,28 +883,28 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>98</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>94.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="I13" s="2">
         <v>8.4</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>2.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -912,28 +912,28 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E14">
         <v>240</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="H14" s="1">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="I14" s="2">
         <v>8.4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1135,13 +1135,13 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1167,13 +1167,13 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1339,13 +1339,13 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1371,13 +1371,13 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1400,13 +1400,13 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1623,28 +1623,28 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>31</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>9.4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1655,28 +1655,28 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>31</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
         <v>9.4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1827,28 +1827,28 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>31</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1859,28 +1859,28 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>98</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>94.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="I13" s="2">
         <v>8.4</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>2.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1888,28 +1888,28 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E14">
         <v>240</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="H14" s="1">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="I14" s="2">
         <v>8.4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
@@ -831,13 +831,13 @@
         <v>14.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -898,13 +898,13 @@
         <v>3.9</v>
       </c>
       <c r="I13" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -930,10 +930,10 @@
         <v>8.4</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1001,25 +1001,25 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1036,25 +1036,25 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1071,25 +1071,25 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1103,25 +1103,25 @@
         <v>97</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F5">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>92.8</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>7.2</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1138,25 +1138,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1170,25 +1170,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1205,25 +1205,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>11.5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1237,25 +1237,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>11.5</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1272,25 +1272,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F10">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1307,25 +1307,25 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>14.8</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1342,25 +1342,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1374,25 +1374,25 @@
         <v>102</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F13">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1403,25 +1403,25 @@
         <v>256</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="F14">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1489,19 +1489,19 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>11.1</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1559,19 +1559,19 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>92.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>7.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1693,19 +1693,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>80.8</v>
+        <v>88.5</v>
       </c>
       <c r="H8" s="1">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1725,19 +1725,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>80.8</v>
+        <v>88.5</v>
       </c>
       <c r="H9" s="1">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1807,13 +1807,13 @@
         <v>14.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1862,25 +1862,25 @@
         <v>102</v>
       </c>
       <c r="E13">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>96.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="I13" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1891,25 +1891,25 @@
         <v>256</v>
       </c>
       <c r="E14">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1524,19 +1524,19 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>88.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="H3" s="1">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1559,19 +1559,19 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>84.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H4" s="1">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1591,19 +1591,19 @@
         <v>97</v>
       </c>
       <c r="E5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>92.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1693,19 +1693,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="H8" s="1">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1725,19 +1725,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="H9" s="1">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1795,19 +1795,19 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>85.2</v>
+        <v>96.3</v>
       </c>
       <c r="H11" s="1">
-        <v>14.8</v>
+        <v>3.7</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1862,16 +1862,16 @@
         <v>102</v>
       </c>
       <c r="E13">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>95.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2">
         <v>8.6</v>
@@ -1891,19 +1891,19 @@
         <v>256</v>
       </c>
       <c r="E14">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>94.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="H14" s="1">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J14">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>3.7</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>3.8</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>2.1</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1705,7 +1705,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>7.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>3.7</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="2">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>2.3</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>9.9</v>
       </c>
       <c r="J14">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20231.xlsx
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>3.7</v>
       </c>
       <c r="I3" s="2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>3.8</v>
       </c>
       <c r="I4" s="2">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>2.1</v>
       </c>
       <c r="I5" s="2">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1693,19 +1693,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1725,19 +1725,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H9" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I9" s="2">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>3.7</v>
       </c>
       <c r="I11" s="2">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="2">
-        <v>9.9</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1891,19 +1891,19 @@
         <v>256</v>
       </c>
       <c r="E14">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="H14" s="1">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="J14">
         <v>0</v>
